--- a/Excel/LoginTestData.xlsx
+++ b/Excel/LoginTestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\đồ án\Test unit\TestProject1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\doantotnghiep\Unit test\Realtime-Auction-Test\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A544FF87-9B42-48AD-AEF8-B3591258FD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7119870E-FE88-48A9-92CD-2D19451F9A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5B6FAD3C-D89D-4A16-B709-E9C25977CD39}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{5B6FAD3C-D89D-4A16-B709-E9C25977CD39}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -120,15 +123,15 @@
     <t>ntpnguyen210104gmail.com</t>
   </si>
   <si>
-    <t>Nguyen@21</t>
-  </si>
-  <si>
     <t>Chào mừng trở lại!
 Đăng nhập thành công</t>
   </si>
   <si>
     <t>Lỗi!
 Sai email hoặc mật khẩu</t>
+  </si>
+  <si>
+    <t>Nguyen21@</t>
   </si>
 </sst>
 </file>
@@ -302,9 +305,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -342,7 +345,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -448,7 +451,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -590,7 +593,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -599,19 +602,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4697040C-621E-4332-80CB-185E1DBB6188}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.44140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="35.5546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="32.109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="40.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="25.44140625" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="25.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="40.85546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -634,7 +637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -645,10 +648,10 @@
         <v>27</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>7</v>
@@ -657,7 +660,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -671,7 +674,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>7</v>
@@ -680,7 +683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -689,10 +692,10 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>7</v>
@@ -701,7 +704,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -712,10 +715,10 @@
         <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>7</v>
@@ -724,7 +727,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
@@ -736,7 +739,7 @@
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>7</v>
@@ -745,7 +748,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -755,7 +758,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="6"/>
       <c r="E7" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>7</v>
@@ -764,7 +767,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -775,10 +778,10 @@
         <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>7</v>
@@ -787,7 +790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -798,10 +801,10 @@
         <v>27</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>32</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>7</v>
